--- a/Running_Log.xlsx
+++ b/Running_Log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adolwick/dolwick_project/biof309project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64E4C0DE-96C2-4A41-9055-5C72F0AE7272}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0DA28F9-EA25-CD4F-A32A-4B746076F9A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3120" yWindow="500" windowWidth="25680" windowHeight="15800" xr2:uid="{4B2E00A5-7125-EC4E-9EAD-C4CEE86B127A}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6051" uniqueCount="4963">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6062" uniqueCount="4969">
   <si>
     <t>Date</t>
   </si>
@@ -14922,6 +14922,24 @@
   </si>
   <si>
     <t>2025-11-22</t>
+  </si>
+  <si>
+    <t>2025-11-24</t>
+  </si>
+  <si>
+    <t>2025-11-28</t>
+  </si>
+  <si>
+    <t>2025-11-30</t>
+  </si>
+  <si>
+    <t>2025-12-03</t>
+  </si>
+  <si>
+    <t>2025-12-05</t>
+  </si>
+  <si>
+    <t>1:04:30</t>
   </si>
 </sst>
 </file>
@@ -15298,7 +15316,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1BECE25-7878-7543-A5E4-1B4438F2AAC2}">
-  <dimension ref="A1:E3624"/>
+  <dimension ref="A1:E3629"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="2"/>
@@ -53223,6 +53241,9 @@
       <c r="B3622" s="1">
         <v>3.75</v>
       </c>
+      <c r="C3622" s="2" t="s">
+        <v>487</v>
+      </c>
     </row>
     <row r="3623" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3623" s="2" t="s">
@@ -53241,6 +53262,61 @@
       </c>
       <c r="B3624" s="1">
         <v>5.79</v>
+      </c>
+    </row>
+    <row r="3625" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3625" s="2" t="s">
+        <v>4963</v>
+      </c>
+      <c r="B3625" s="1">
+        <v>4.29</v>
+      </c>
+      <c r="C3625" s="2" t="s">
+        <v>4253</v>
+      </c>
+    </row>
+    <row r="3626" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3626" s="2" t="s">
+        <v>4964</v>
+      </c>
+      <c r="B3626" s="1">
+        <v>5.75</v>
+      </c>
+      <c r="C3626" s="2" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="3627" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3627" s="2" t="s">
+        <v>4965</v>
+      </c>
+      <c r="B3627" s="1">
+        <v>5.5</v>
+      </c>
+      <c r="C3627" s="2" t="s">
+        <v>3715</v>
+      </c>
+    </row>
+    <row r="3628" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3628" s="2" t="s">
+        <v>4966</v>
+      </c>
+      <c r="B3628" s="1">
+        <v>5.28</v>
+      </c>
+      <c r="C3628" s="2" t="s">
+        <v>3357</v>
+      </c>
+    </row>
+    <row r="3629" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3629" s="2" t="s">
+        <v>4967</v>
+      </c>
+      <c r="B3629" s="1">
+        <v>8.8800000000000008</v>
+      </c>
+      <c r="C3629" s="2" t="s">
+        <v>4968</v>
       </c>
     </row>
   </sheetData>
